--- a/MOSFETAmp/MOSFETAmp.xlsx
+++ b/MOSFETAmp/MOSFETAmp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomwatson/Documents/GitHub/Kicadprojects/MOSFETAmp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD0EEF5-0C02-BD4C-80F7-20B751E439C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A55A75F-69CA-5C4B-BB2A-5668E212025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10680" yWindow="3220" windowWidth="27640" windowHeight="16680" xr2:uid="{20460DA5-3CA5-BD4B-856F-B9E99E29A5BE}"/>
+    <workbookView xWindow="6560" yWindow="3220" windowWidth="27640" windowHeight="16680" xr2:uid="{20460DA5-3CA5-BD4B-856F-B9E99E29A5BE}"/>
   </bookViews>
   <sheets>
     <sheet name="MOSFETAmp" sheetId="1" r:id="rId1"/>
@@ -1454,23 +1454,23 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>104</v>
       </c>
     </row>
